--- a/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-09-19).xlsx
+++ b/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-09-19).xlsx
@@ -935,22 +935,22 @@
     <t>214</t>
   </si>
   <si>
-    <t>32</t>
-  </si>
-  <si>
-    <t>R$ 9.292,84</t>
-  </si>
-  <si>
-    <t>96.9</t>
-  </si>
-  <si>
-    <t>61.5</t>
-  </si>
-  <si>
-    <t>6.34</t>
-  </si>
-  <si>
-    <t>21.6</t>
+    <t>29</t>
+  </si>
+  <si>
+    <t>R$ 9.297,00</t>
+  </si>
+  <si>
+    <t>97.1</t>
+  </si>
+  <si>
+    <t>61.4</t>
+  </si>
+  <si>
+    <t>6.32</t>
+  </si>
+  <si>
+    <t>21.5</t>
   </si>
   <si>
     <t>8.5</t>
@@ -959,10 +959,10 @@
     <t>6.1</t>
   </si>
   <si>
-    <t>33.8%</t>
-  </si>
-  <si>
-    <t>17.0%</t>
+    <t>34.3%</t>
+  </si>
+  <si>
+    <t>16.9%</t>
   </si>
   <si>
     <t>1.5%</t>
@@ -989,19 +989,19 @@
     <t>4.6%</t>
   </si>
   <si>
-    <t>2203.0</t>
-  </si>
-  <si>
-    <t>1877.0</t>
-  </si>
-  <si>
-    <t>171.0</t>
+    <t>2211.0</t>
+  </si>
+  <si>
+    <t>1884.0</t>
+  </si>
+  <si>
+    <t>172.0</t>
   </si>
   <si>
     <t>31.0</t>
   </si>
   <si>
-    <t>374.0</t>
+    <t>379.0</t>
   </si>
   <si>
     <t>114.0</t>
@@ -1010,7 +1010,7 @@
     <t>17.0</t>
   </si>
   <si>
-    <t>673.0</t>
+    <t>675.0</t>
   </si>
   <si>
     <t>281.0</t>
@@ -10065,7 +10065,7 @@
         <v>19618</v>
       </c>
       <c r="B58" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C58" s="4">
         <v>51</v>
@@ -10095,14 +10095,26 @@
         <v>58</v>
       </c>
       <c r="L58" s="4"/>
-      <c r="M58" s="5"/>
-      <c r="N58" s="6"/>
+      <c r="M58" s="5">
+        <v>12444.1</v>
+      </c>
+      <c r="N58" s="6">
+        <v>137</v>
+      </c>
       <c r="O58" s="6"/>
-      <c r="P58" s="7"/>
-      <c r="Q58" s="8"/>
-      <c r="R58" s="8"/>
+      <c r="P58" s="7">
+        <v>6.6127737226277379</v>
+      </c>
+      <c r="Q58" s="8">
+        <v>22.408254285714285</v>
+      </c>
+      <c r="R58" s="8">
+        <v>8.0538095238095231</v>
+      </c>
       <c r="S58" s="8"/>
-      <c r="T58" s="9"/>
+      <c r="T58" s="9">
+        <v>0.22857142857142856</v>
+      </c>
       <c r="U58" s="9"/>
       <c r="V58" s="9"/>
       <c r="W58" s="9"/>
@@ -26961,7 +26973,7 @@
         <v>19890</v>
       </c>
       <c r="B172" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C172" s="4">
         <v>51</v>
@@ -26991,35 +27003,93 @@
         <v>58</v>
       </c>
       <c r="L172" s="4"/>
-      <c r="M172" s="5"/>
-      <c r="N172" s="6"/>
-      <c r="O172" s="6"/>
-      <c r="P172" s="7"/>
-      <c r="Q172" s="8"/>
-      <c r="R172" s="8"/>
-      <c r="S172" s="8"/>
-      <c r="T172" s="9"/>
-      <c r="U172" s="9"/>
-      <c r="V172" s="9"/>
-      <c r="W172" s="9"/>
-      <c r="X172" s="9"/>
-      <c r="Y172" s="9"/>
-      <c r="Z172" s="9"/>
-      <c r="AA172" s="9"/>
-      <c r="AB172" s="9"/>
-      <c r="AC172" s="9"/>
-      <c r="AD172" s="6"/>
-      <c r="AE172" s="6"/>
-      <c r="AF172" s="6"/>
-      <c r="AG172" s="6"/>
-      <c r="AH172" s="6"/>
-      <c r="AI172" s="6"/>
-      <c r="AJ172" s="6"/>
-      <c r="AK172" s="6"/>
-      <c r="AL172" s="6"/>
-      <c r="AM172" s="6"/>
-      <c r="AN172" s="9"/>
-      <c r="AO172" s="6"/>
+      <c r="M172" s="5">
+        <v>5644.6700000000001</v>
+      </c>
+      <c r="N172" s="6">
+        <v>63</v>
+      </c>
+      <c r="O172" s="6">
+        <v>53</v>
+      </c>
+      <c r="P172" s="7">
+        <v>4.4048387096774198</v>
+      </c>
+      <c r="Q172" s="8">
+        <v>14.746226415094339</v>
+      </c>
+      <c r="R172" s="8">
+        <v>3.3389943396226416</v>
+      </c>
+      <c r="S172" s="8">
+        <v>7</v>
+      </c>
+      <c r="T172" s="9">
+        <v>0.60377358490566035</v>
+      </c>
+      <c r="U172" s="9">
+        <v>0.13207547169811321</v>
+      </c>
+      <c r="V172" s="9">
+        <v>0.018867924528301886</v>
+      </c>
+      <c r="W172" s="9">
+        <v>0</v>
+      </c>
+      <c r="X172" s="9">
+        <v>0.094339622641509441</v>
+      </c>
+      <c r="Y172" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z172" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA172" s="9">
+        <v>0.037735849056603772</v>
+      </c>
+      <c r="AB172" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC172" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD172" s="6">
+        <v>8</v>
+      </c>
+      <c r="AE172" s="6">
+        <v>7</v>
+      </c>
+      <c r="AF172" s="6">
+        <v>1</v>
+      </c>
+      <c r="AG172" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH172" s="6">
+        <v>5</v>
+      </c>
+      <c r="AI172" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ172" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK172" s="6">
+        <v>2</v>
+      </c>
+      <c r="AL172" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM172" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN172" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO172" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP172" s="4">
         <v>58</v>
       </c>
@@ -30400,7 +30470,7 @@
         <v>19944</v>
       </c>
       <c r="B195" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C195" s="4">
         <v>51</v>
@@ -30430,14 +30500,26 @@
         <v>58</v>
       </c>
       <c r="L195" s="4"/>
-      <c r="M195" s="5"/>
-      <c r="N195" s="6"/>
+      <c r="M195" s="5">
+        <v>10559.5</v>
+      </c>
+      <c r="N195" s="6">
+        <v>121</v>
+      </c>
       <c r="O195" s="6"/>
-      <c r="P195" s="7"/>
-      <c r="Q195" s="8"/>
-      <c r="R195" s="8"/>
+      <c r="P195" s="7">
+        <v>5.6540178571428568</v>
+      </c>
+      <c r="Q195" s="8">
+        <v>22.17970128205128</v>
+      </c>
+      <c r="R195" s="8">
+        <v>9.6119653846153845</v>
+      </c>
       <c r="S195" s="8"/>
-      <c r="T195" s="9"/>
+      <c r="T195" s="9">
+        <v>0.20512820512820512</v>
+      </c>
       <c r="U195" s="9"/>
       <c r="V195" s="9"/>
       <c r="W195" s="9"/>

--- a/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-09-19).xlsx
+++ b/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-09-19).xlsx
@@ -935,34 +935,34 @@
     <t>214</t>
   </si>
   <si>
-    <t>29</t>
-  </si>
-  <si>
-    <t>R$ 9.297,00</t>
-  </si>
-  <si>
-    <t>97.1</t>
-  </si>
-  <si>
-    <t>61.4</t>
+    <t>28</t>
+  </si>
+  <si>
+    <t>R$ 9.287,52</t>
+  </si>
+  <si>
+    <t>97.0</t>
+  </si>
+  <si>
+    <t>61.8</t>
   </si>
   <si>
     <t>6.32</t>
   </si>
   <si>
-    <t>21.5</t>
+    <t>21.6</t>
   </si>
   <si>
     <t>8.5</t>
   </si>
   <si>
-    <t>6.1</t>
-  </si>
-  <si>
-    <t>34.3%</t>
-  </si>
-  <si>
-    <t>16.9%</t>
+    <t>6.2</t>
+  </si>
+  <si>
+    <t>33.5%</t>
+  </si>
+  <si>
+    <t>17.0%</t>
   </si>
   <si>
     <t>1.5%</t>
@@ -971,37 +971,37 @@
     <t>0.3%</t>
   </si>
   <si>
-    <t>3.4%</t>
+    <t>3.3%</t>
   </si>
   <si>
     <t>1.0%</t>
   </si>
   <si>
-    <t>0.2%</t>
-  </si>
-  <si>
-    <t>6.1%</t>
+    <t>0.1%</t>
+  </si>
+  <si>
+    <t>6.0%</t>
   </si>
   <si>
     <t>2.5%</t>
   </si>
   <si>
-    <t>4.6%</t>
-  </si>
-  <si>
-    <t>2211.0</t>
-  </si>
-  <si>
-    <t>1884.0</t>
-  </si>
-  <si>
-    <t>172.0</t>
+    <t>4.7%</t>
+  </si>
+  <si>
+    <t>2271.0</t>
+  </si>
+  <si>
+    <t>1937.0</t>
+  </si>
+  <si>
+    <t>177.0</t>
   </si>
   <si>
     <t>31.0</t>
   </si>
   <si>
-    <t>379.0</t>
+    <t>381.0</t>
   </si>
   <si>
     <t>114.0</t>
@@ -1010,19 +1010,19 @@
     <t>17.0</t>
   </si>
   <si>
-    <t>675.0</t>
-  </si>
-  <si>
-    <t>281.0</t>
-  </si>
-  <si>
-    <t>506.0</t>
+    <t>687.0</t>
+  </si>
+  <si>
+    <t>287.0</t>
+  </si>
+  <si>
+    <t>535.0</t>
   </si>
   <si>
     <t>0.6%</t>
   </si>
   <si>
-    <t>67.0</t>
+    <t>73.0</t>
   </si>
   <si>
     <t>1</t>
@@ -3278,7 +3278,9 @@
       <c r="N13" s="6">
         <v>116</v>
       </c>
-      <c r="O13" s="6"/>
+      <c r="O13" s="6">
+        <v>93</v>
+      </c>
       <c r="P13" s="7">
         <v>9.9851694915254239</v>
       </c>
@@ -3288,31 +3290,75 @@
       <c r="R13" s="8">
         <v>9.4508956989247324</v>
       </c>
-      <c r="S13" s="8"/>
+      <c r="S13" s="8">
+        <v>7</v>
+      </c>
       <c r="T13" s="9">
         <v>0.15053763440860216</v>
       </c>
-      <c r="U13" s="9"/>
-      <c r="V13" s="9"/>
-      <c r="W13" s="9"/>
-      <c r="X13" s="9"/>
-      <c r="Y13" s="9"/>
-      <c r="Z13" s="9"/>
-      <c r="AA13" s="9"/>
-      <c r="AB13" s="9"/>
-      <c r="AC13" s="9"/>
-      <c r="AD13" s="6"/>
-      <c r="AE13" s="6"/>
-      <c r="AF13" s="6"/>
-      <c r="AG13" s="6"/>
-      <c r="AH13" s="6"/>
-      <c r="AI13" s="6"/>
-      <c r="AJ13" s="6"/>
-      <c r="AK13" s="6"/>
-      <c r="AL13" s="6"/>
-      <c r="AM13" s="6"/>
-      <c r="AN13" s="9"/>
-      <c r="AO13" s="6"/>
+      <c r="U13" s="9">
+        <v>0.19354838709677419</v>
+      </c>
+      <c r="V13" s="9">
+        <v>0</v>
+      </c>
+      <c r="W13" s="9">
+        <v>0</v>
+      </c>
+      <c r="X13" s="9">
+        <v>0.021505376344086023</v>
+      </c>
+      <c r="Y13" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z13" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA13" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB13" s="9">
+        <v>0.032258064516129031</v>
+      </c>
+      <c r="AC13" s="9">
+        <v>0.086021505376344093</v>
+      </c>
+      <c r="AD13" s="6">
+        <v>19</v>
+      </c>
+      <c r="AE13" s="6">
+        <v>18</v>
+      </c>
+      <c r="AF13" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG13" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH13" s="6">
+        <v>2</v>
+      </c>
+      <c r="AI13" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ13" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK13" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL13" s="6">
+        <v>3</v>
+      </c>
+      <c r="AM13" s="6">
+        <v>8</v>
+      </c>
+      <c r="AN13" s="9">
+        <v>0.064516129032258063</v>
+      </c>
+      <c r="AO13" s="6">
+        <v>6</v>
+      </c>
       <c t="s" r="AP13" s="4">
         <v>58</v>
       </c>
@@ -10101,7 +10147,9 @@
       <c r="N58" s="6">
         <v>137</v>
       </c>
-      <c r="O58" s="6"/>
+      <c r="O58" s="6">
+        <v>105</v>
+      </c>
       <c r="P58" s="7">
         <v>6.6127737226277379</v>
       </c>
@@ -10111,31 +10159,75 @@
       <c r="R58" s="8">
         <v>8.0538095238095231</v>
       </c>
-      <c r="S58" s="8"/>
+      <c r="S58" s="8">
+        <v>7</v>
+      </c>
       <c r="T58" s="9">
         <v>0.22857142857142856</v>
       </c>
-      <c r="U58" s="9"/>
-      <c r="V58" s="9"/>
-      <c r="W58" s="9"/>
-      <c r="X58" s="9"/>
-      <c r="Y58" s="9"/>
-      <c r="Z58" s="9"/>
-      <c r="AA58" s="9"/>
-      <c r="AB58" s="9"/>
-      <c r="AC58" s="9"/>
-      <c r="AD58" s="6"/>
-      <c r="AE58" s="6"/>
-      <c r="AF58" s="6"/>
-      <c r="AG58" s="6"/>
-      <c r="AH58" s="6"/>
-      <c r="AI58" s="6"/>
-      <c r="AJ58" s="6"/>
-      <c r="AK58" s="6"/>
-      <c r="AL58" s="6"/>
-      <c r="AM58" s="6"/>
-      <c r="AN58" s="9"/>
-      <c r="AO58" s="6"/>
+      <c r="U58" s="9">
+        <v>0.095238095238095233</v>
+      </c>
+      <c r="V58" s="9">
+        <v>0.028571428571428571</v>
+      </c>
+      <c r="W58" s="9">
+        <v>0</v>
+      </c>
+      <c r="X58" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y58" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z58" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA58" s="9">
+        <v>0.0095238095238095247</v>
+      </c>
+      <c r="AB58" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC58" s="9">
+        <v>0.057142857142857141</v>
+      </c>
+      <c r="AD58" s="6">
+        <v>10</v>
+      </c>
+      <c r="AE58" s="6">
+        <v>10</v>
+      </c>
+      <c r="AF58" s="6">
+        <v>3</v>
+      </c>
+      <c r="AG58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK58" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM58" s="6">
+        <v>6</v>
+      </c>
+      <c r="AN58" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO58" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP58" s="4">
         <v>58</v>
       </c>
@@ -12711,7 +12803,7 @@
         <v>19661</v>
       </c>
       <c r="B76" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C76" s="4">
         <v>51</v>
@@ -12739,35 +12831,93 @@
         <v>58</v>
       </c>
       <c r="L76" s="4"/>
-      <c r="M76" s="5"/>
-      <c r="N76" s="6"/>
-      <c r="O76" s="6"/>
-      <c r="P76" s="7"/>
-      <c r="Q76" s="8"/>
-      <c r="R76" s="8"/>
-      <c r="S76" s="8"/>
-      <c r="T76" s="9"/>
-      <c r="U76" s="9"/>
-      <c r="V76" s="9"/>
-      <c r="W76" s="9"/>
-      <c r="X76" s="9"/>
-      <c r="Y76" s="9"/>
-      <c r="Z76" s="9"/>
-      <c r="AA76" s="9"/>
-      <c r="AB76" s="9"/>
-      <c r="AC76" s="9"/>
-      <c r="AD76" s="6"/>
-      <c r="AE76" s="6"/>
-      <c r="AF76" s="6"/>
-      <c r="AG76" s="6"/>
-      <c r="AH76" s="6"/>
-      <c r="AI76" s="6"/>
-      <c r="AJ76" s="6"/>
-      <c r="AK76" s="6"/>
-      <c r="AL76" s="6"/>
-      <c r="AM76" s="6"/>
-      <c r="AN76" s="9"/>
-      <c r="AO76" s="6"/>
+      <c r="M76" s="5">
+        <v>7535.2799999999997</v>
+      </c>
+      <c r="N76" s="6">
+        <v>87</v>
+      </c>
+      <c r="O76" s="6">
+        <v>52</v>
+      </c>
+      <c r="P76" s="7">
+        <v>6.3384123809523816</v>
+      </c>
+      <c r="Q76" s="8">
+        <v>23.591667307692305</v>
+      </c>
+      <c r="R76" s="8">
+        <v>9.3939723404255329</v>
+      </c>
+      <c r="S76" s="8">
+        <v>9</v>
+      </c>
+      <c r="T76" s="9">
+        <v>0.28846153846153844</v>
+      </c>
+      <c r="U76" s="9">
+        <v>0.46153846153846156</v>
+      </c>
+      <c r="V76" s="9">
+        <v>0.038461538461538464</v>
+      </c>
+      <c r="W76" s="9">
+        <v>0</v>
+      </c>
+      <c r="X76" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y76" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z76" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA76" s="9">
+        <v>0.19230769230769232</v>
+      </c>
+      <c r="AB76" s="9">
+        <v>0.057692307692307696</v>
+      </c>
+      <c r="AC76" s="9">
+        <v>0.28846153846153844</v>
+      </c>
+      <c r="AD76" s="6">
+        <v>30</v>
+      </c>
+      <c r="AE76" s="6">
+        <v>24</v>
+      </c>
+      <c r="AF76" s="6">
+        <v>2</v>
+      </c>
+      <c r="AG76" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH76" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI76" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ76" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK76" s="6">
+        <v>10</v>
+      </c>
+      <c r="AL76" s="6">
+        <v>3</v>
+      </c>
+      <c r="AM76" s="6">
+        <v>15</v>
+      </c>
+      <c r="AN76" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO76" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP76" s="4">
         <v>58</v>
       </c>
@@ -28102,7 +28252,9 @@
       <c r="N179" s="6">
         <v>113</v>
       </c>
-      <c r="O179" s="6"/>
+      <c r="O179" s="6">
+        <v>59</v>
+      </c>
       <c r="P179" s="7">
         <v>4.5783185840707965</v>
       </c>
@@ -28112,31 +28264,75 @@
       <c r="R179" s="8">
         <v>1.9197745762711864</v>
       </c>
-      <c r="S179" s="8"/>
+      <c r="S179" s="8">
+        <v>7</v>
+      </c>
       <c r="T179" s="9">
         <v>0.81355932203389836</v>
       </c>
-      <c r="U179" s="9"/>
-      <c r="V179" s="9"/>
-      <c r="W179" s="9"/>
-      <c r="X179" s="9"/>
-      <c r="Y179" s="9"/>
-      <c r="Z179" s="9"/>
-      <c r="AA179" s="9"/>
-      <c r="AB179" s="9"/>
-      <c r="AC179" s="9"/>
-      <c r="AD179" s="6"/>
-      <c r="AE179" s="6"/>
-      <c r="AF179" s="6"/>
-      <c r="AG179" s="6"/>
-      <c r="AH179" s="6"/>
-      <c r="AI179" s="6"/>
-      <c r="AJ179" s="6"/>
-      <c r="AK179" s="6"/>
-      <c r="AL179" s="6"/>
-      <c r="AM179" s="6"/>
-      <c r="AN179" s="9"/>
-      <c r="AO179" s="6"/>
+      <c r="U179" s="9">
+        <v>0.016949152542372881</v>
+      </c>
+      <c r="V179" s="9">
+        <v>0</v>
+      </c>
+      <c r="W179" s="9">
+        <v>0</v>
+      </c>
+      <c r="X179" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y179" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z179" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA179" s="9">
+        <v>0.016949152542372881</v>
+      </c>
+      <c r="AB179" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC179" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD179" s="6">
+        <v>1</v>
+      </c>
+      <c r="AE179" s="6">
+        <v>1</v>
+      </c>
+      <c r="AF179" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG179" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH179" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI179" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ179" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK179" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL179" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM179" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN179" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO179" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP179" s="4">
         <v>58</v>
       </c>

--- a/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-09-19).xlsx
+++ b/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-09-19).xlsx
@@ -935,34 +935,34 @@
     <t>214</t>
   </si>
   <si>
-    <t>28</t>
+    <t>22</t>
   </si>
   <si>
-    <t>R$ 9.287,52</t>
+    <t>R$ 9.293,80</t>
   </si>
   <si>
-    <t>97.0</t>
+    <t>96.9</t>
   </si>
   <si>
-    <t>61.8</t>
+    <t>61.9</t>
   </si>
   <si>
-    <t>6.32</t>
+    <t>6.30</t>
   </si>
   <si>
-    <t>21.6</t>
+    <t>21.5</t>
   </si>
   <si>
     <t>8.5</t>
   </si>
   <si>
-    <t>6.2</t>
+    <t>6.4</t>
   </si>
   <si>
     <t>33.5%</t>
   </si>
   <si>
-    <t>17.0%</t>
+    <t>16.6%</t>
   </si>
   <si>
     <t>1.5%</t>
@@ -971,7 +971,7 @@
     <t>0.3%</t>
   </si>
   <si>
-    <t>3.3%</t>
+    <t>3.2%</t>
   </si>
   <si>
     <t>1.0%</t>
@@ -980,19 +980,19 @@
     <t>0.1%</t>
   </si>
   <si>
-    <t>6.0%</t>
+    <t>5.9%</t>
   </si>
   <si>
-    <t>2.5%</t>
+    <t>2.4%</t>
   </si>
   <si>
-    <t>4.7%</t>
+    <t>4.6%</t>
   </si>
   <si>
-    <t>2271.0</t>
+    <t>2289.0</t>
   </si>
   <si>
-    <t>1937.0</t>
+    <t>1954.0</t>
   </si>
   <si>
     <t>177.0</t>
@@ -1010,13 +1010,13 @@
     <t>17.0</t>
   </si>
   <si>
-    <t>687.0</t>
+    <t>694.0</t>
   </si>
   <si>
-    <t>287.0</t>
+    <t>288.0</t>
   </si>
   <si>
-    <t>535.0</t>
+    <t>545.0</t>
   </si>
   <si>
     <t>0.6%</t>
@@ -2209,7 +2209,7 @@
         <v>19507</v>
       </c>
       <c r="B6" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C6" s="4">
         <v>51</v>
@@ -2239,35 +2239,93 @@
         <v>58</v>
       </c>
       <c r="L6" s="4"/>
-      <c r="M6" s="5"/>
-      <c r="N6" s="6"/>
-      <c r="O6" s="6"/>
-      <c r="P6" s="7"/>
-      <c r="Q6" s="8"/>
-      <c r="R6" s="8"/>
-      <c r="S6" s="8"/>
-      <c r="T6" s="9"/>
-      <c r="U6" s="9"/>
-      <c r="V6" s="9"/>
-      <c r="W6" s="9"/>
-      <c r="X6" s="9"/>
-      <c r="Y6" s="9"/>
-      <c r="Z6" s="9"/>
-      <c r="AA6" s="9"/>
-      <c r="AB6" s="9"/>
-      <c r="AC6" s="9"/>
-      <c r="AD6" s="6"/>
-      <c r="AE6" s="6"/>
-      <c r="AF6" s="6"/>
-      <c r="AG6" s="6"/>
-      <c r="AH6" s="6"/>
-      <c r="AI6" s="6"/>
-      <c r="AJ6" s="6"/>
-      <c r="AK6" s="6"/>
-      <c r="AL6" s="6"/>
-      <c r="AM6" s="6"/>
-      <c r="AN6" s="9"/>
-      <c r="AO6" s="6"/>
+      <c r="M6" s="5">
+        <v>19175.549999999999</v>
+      </c>
+      <c r="N6" s="6">
+        <v>174</v>
+      </c>
+      <c r="O6" s="6">
+        <v>139</v>
+      </c>
+      <c r="P6" s="7">
+        <v>7.0841954022988514</v>
+      </c>
+      <c r="Q6" s="8">
+        <v>16.12338129496403</v>
+      </c>
+      <c r="R6" s="8">
+        <v>2.2324817518248179</v>
+      </c>
+      <c r="S6" s="8">
+        <v>7</v>
+      </c>
+      <c r="T6" s="9">
+        <v>0.53237410071942448</v>
+      </c>
+      <c r="U6" s="9">
+        <v>0.050359712230215826</v>
+      </c>
+      <c r="V6" s="9">
+        <v>0</v>
+      </c>
+      <c r="W6" s="9">
+        <v>0</v>
+      </c>
+      <c r="X6" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y6" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z6" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA6" s="9">
+        <v>0.021582733812949641</v>
+      </c>
+      <c r="AB6" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC6" s="9">
+        <v>0.028776978417266189</v>
+      </c>
+      <c r="AD6" s="6">
+        <v>7</v>
+      </c>
+      <c r="AE6" s="6">
+        <v>7</v>
+      </c>
+      <c r="AF6" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG6" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH6" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI6" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ6" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK6" s="6">
+        <v>3</v>
+      </c>
+      <c r="AL6" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM6" s="6">
+        <v>4</v>
+      </c>
+      <c r="AN6" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO6" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP6" s="4">
         <v>58</v>
       </c>
@@ -4961,7 +5019,7 @@
         <v>19536</v>
       </c>
       <c r="B24" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C24" s="4">
         <v>51</v>
@@ -4991,14 +5049,26 @@
         <v>58</v>
       </c>
       <c r="L24" s="4"/>
-      <c r="M24" s="5"/>
-      <c r="N24" s="6"/>
+      <c r="M24" s="5">
+        <v>11835.200000000001</v>
+      </c>
+      <c r="N24" s="6">
+        <v>132</v>
+      </c>
       <c r="O24" s="6"/>
-      <c r="P24" s="7"/>
-      <c r="Q24" s="8"/>
-      <c r="R24" s="8"/>
+      <c r="P24" s="7">
+        <v>5.2045217054263562</v>
+      </c>
+      <c r="Q24" s="8">
+        <v>21.506179775280899</v>
+      </c>
+      <c r="R24" s="8">
+        <v>9.5113636363636367</v>
+      </c>
       <c r="S24" s="8"/>
-      <c r="T24" s="9"/>
+      <c r="T24" s="9">
+        <v>0.1348314606741573</v>
+      </c>
       <c r="U24" s="9"/>
       <c r="V24" s="9"/>
       <c r="W24" s="9"/>
@@ -6785,7 +6855,7 @@
         <v>19562</v>
       </c>
       <c r="B36" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C36" s="4">
         <v>51</v>
@@ -6815,35 +6885,93 @@
         <v>58</v>
       </c>
       <c r="L36" s="4"/>
-      <c r="M36" s="5"/>
-      <c r="N36" s="6"/>
-      <c r="O36" s="6"/>
-      <c r="P36" s="7"/>
-      <c r="Q36" s="8"/>
-      <c r="R36" s="8"/>
-      <c r="S36" s="8"/>
-      <c r="T36" s="9"/>
-      <c r="U36" s="9"/>
-      <c r="V36" s="9"/>
-      <c r="W36" s="9"/>
-      <c r="X36" s="9"/>
-      <c r="Y36" s="9"/>
-      <c r="Z36" s="9"/>
-      <c r="AA36" s="9"/>
-      <c r="AB36" s="9"/>
-      <c r="AC36" s="9"/>
-      <c r="AD36" s="6"/>
-      <c r="AE36" s="6"/>
-      <c r="AF36" s="6"/>
-      <c r="AG36" s="6"/>
-      <c r="AH36" s="6"/>
-      <c r="AI36" s="6"/>
-      <c r="AJ36" s="6"/>
-      <c r="AK36" s="6"/>
-      <c r="AL36" s="6"/>
-      <c r="AM36" s="6"/>
-      <c r="AN36" s="9"/>
-      <c r="AO36" s="6"/>
+      <c r="M36" s="5">
+        <v>8344.25</v>
+      </c>
+      <c r="N36" s="6">
+        <v>77</v>
+      </c>
+      <c r="O36" s="6">
+        <v>52</v>
+      </c>
+      <c r="P36" s="7">
+        <v>6.6346486842105259</v>
+      </c>
+      <c r="Q36" s="8">
+        <v>21.263461538461538</v>
+      </c>
+      <c r="R36" s="8">
+        <v>7.325162745098039</v>
+      </c>
+      <c r="S36" s="8">
+        <v>7</v>
+      </c>
+      <c r="T36" s="9">
+        <v>0.17307692307692307</v>
+      </c>
+      <c r="U36" s="9">
+        <v>0.057692307692307696</v>
+      </c>
+      <c r="V36" s="9">
+        <v>0</v>
+      </c>
+      <c r="W36" s="9">
+        <v>0</v>
+      </c>
+      <c r="X36" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y36" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z36" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA36" s="9">
+        <v>0.057692307692307696</v>
+      </c>
+      <c r="AB36" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC36" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD36" s="6">
+        <v>3</v>
+      </c>
+      <c r="AE36" s="6">
+        <v>3</v>
+      </c>
+      <c r="AF36" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG36" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH36" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI36" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ36" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK36" s="6">
+        <v>3</v>
+      </c>
+      <c r="AL36" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM36" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN36" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO36" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP36" s="4">
         <v>58</v>
       </c>
@@ -7088,7 +7216,7 @@
         <v>8.1057465517241383</v>
       </c>
       <c r="S38" s="8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T38" s="9">
         <v>0.34999999999999998</v>
@@ -9074,7 +9202,7 @@
         <v>19602</v>
       </c>
       <c r="B51" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C51" s="4">
         <v>51</v>
@@ -9104,35 +9232,93 @@
         <v>58</v>
       </c>
       <c r="L51" s="4"/>
-      <c r="M51" s="5"/>
-      <c r="N51" s="6"/>
-      <c r="O51" s="6"/>
-      <c r="P51" s="7"/>
-      <c r="Q51" s="8"/>
-      <c r="R51" s="8"/>
-      <c r="S51" s="8"/>
-      <c r="T51" s="9"/>
-      <c r="U51" s="9"/>
-      <c r="V51" s="9"/>
-      <c r="W51" s="9"/>
-      <c r="X51" s="9"/>
-      <c r="Y51" s="9"/>
-      <c r="Z51" s="9"/>
-      <c r="AA51" s="9"/>
-      <c r="AB51" s="9"/>
-      <c r="AC51" s="9"/>
-      <c r="AD51" s="6"/>
-      <c r="AE51" s="6"/>
-      <c r="AF51" s="6"/>
-      <c r="AG51" s="6"/>
-      <c r="AH51" s="6"/>
-      <c r="AI51" s="6"/>
-      <c r="AJ51" s="6"/>
-      <c r="AK51" s="6"/>
-      <c r="AL51" s="6"/>
-      <c r="AM51" s="6"/>
-      <c r="AN51" s="9"/>
-      <c r="AO51" s="6"/>
+      <c r="M51" s="5">
+        <v>1551.28</v>
+      </c>
+      <c r="N51" s="6">
+        <v>12</v>
+      </c>
+      <c r="O51" s="6">
+        <v>7</v>
+      </c>
+      <c r="P51" s="7">
+        <v>5.2902750000000003</v>
+      </c>
+      <c r="Q51" s="8">
+        <v>25.145242857142854</v>
+      </c>
+      <c r="R51" s="8">
+        <v>14.983333333333334</v>
+      </c>
+      <c r="S51" s="8">
+        <v>7</v>
+      </c>
+      <c r="T51" s="9">
+        <v>0</v>
+      </c>
+      <c r="U51" s="9">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="V51" s="9">
+        <v>0</v>
+      </c>
+      <c r="W51" s="9">
+        <v>0</v>
+      </c>
+      <c r="X51" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y51" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z51" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA51" s="9">
+        <v>0.14285714285714285</v>
+      </c>
+      <c r="AB51" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC51" s="9">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="AD51" s="6">
+        <v>3</v>
+      </c>
+      <c r="AE51" s="6">
+        <v>2</v>
+      </c>
+      <c r="AF51" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG51" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH51" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI51" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ51" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK51" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL51" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM51" s="6">
+        <v>2</v>
+      </c>
+      <c r="AN51" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO51" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP51" s="4">
         <v>58</v>
       </c>
@@ -14776,7 +14962,7 @@
         <v>19693</v>
       </c>
       <c r="B89" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C89" s="4">
         <v>51</v>
@@ -14804,14 +14990,26 @@
         <v>58</v>
       </c>
       <c r="L89" s="4"/>
-      <c r="M89" s="5"/>
-      <c r="N89" s="6"/>
+      <c r="M89" s="5">
+        <v>9518.8299999999999</v>
+      </c>
+      <c r="N89" s="6">
+        <v>89</v>
+      </c>
       <c r="O89" s="6"/>
-      <c r="P89" s="7"/>
-      <c r="Q89" s="8"/>
-      <c r="R89" s="8"/>
+      <c r="P89" s="7">
+        <v>3.8782054945054942</v>
+      </c>
+      <c r="Q89" s="8">
+        <v>17.946191428571428</v>
+      </c>
+      <c r="R89" s="8">
+        <v>5.9607852941176471</v>
+      </c>
       <c r="S89" s="8"/>
-      <c r="T89" s="9"/>
+      <c r="T89" s="9">
+        <v>0.22857142857142856</v>
+      </c>
       <c r="U89" s="9"/>
       <c r="V89" s="9"/>
       <c r="W89" s="9"/>
@@ -25047,7 +25245,7 @@
         <v>19859</v>
       </c>
       <c r="B158" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C158" s="4">
         <v>51</v>
@@ -25077,35 +25275,93 @@
         <v>58</v>
       </c>
       <c r="L158" s="4"/>
-      <c r="M158" s="5"/>
-      <c r="N158" s="6"/>
-      <c r="O158" s="6"/>
-      <c r="P158" s="7"/>
-      <c r="Q158" s="8"/>
-      <c r="R158" s="8"/>
-      <c r="S158" s="8"/>
-      <c r="T158" s="9"/>
-      <c r="U158" s="9"/>
-      <c r="V158" s="9"/>
-      <c r="W158" s="9"/>
-      <c r="X158" s="9"/>
-      <c r="Y158" s="9"/>
-      <c r="Z158" s="9"/>
-      <c r="AA158" s="9"/>
-      <c r="AB158" s="9"/>
-      <c r="AC158" s="9"/>
-      <c r="AD158" s="6"/>
-      <c r="AE158" s="6"/>
-      <c r="AF158" s="6"/>
-      <c r="AG158" s="6"/>
-      <c r="AH158" s="6"/>
-      <c r="AI158" s="6"/>
-      <c r="AJ158" s="6"/>
-      <c r="AK158" s="6"/>
-      <c r="AL158" s="6"/>
-      <c r="AM158" s="6"/>
-      <c r="AN158" s="9"/>
-      <c r="AO158" s="6"/>
+      <c r="M158" s="5">
+        <v>6504.3900000000003</v>
+      </c>
+      <c r="N158" s="6">
+        <v>67</v>
+      </c>
+      <c r="O158" s="6">
+        <v>54</v>
+      </c>
+      <c r="P158" s="7">
+        <v>5.8121212121212125</v>
+      </c>
+      <c r="Q158" s="8">
+        <v>20.083333333333332</v>
+      </c>
+      <c r="R158" s="8">
+        <v>6.9981481481481476</v>
+      </c>
+      <c r="S158" s="8">
+        <v>7</v>
+      </c>
+      <c r="T158" s="9">
+        <v>0.24074074074074073</v>
+      </c>
+      <c r="U158" s="9">
+        <v>0</v>
+      </c>
+      <c r="V158" s="9">
+        <v>0</v>
+      </c>
+      <c r="W158" s="9">
+        <v>0</v>
+      </c>
+      <c r="X158" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y158" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z158" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA158" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB158" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC158" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AE158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AF158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN158" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO158" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP158" s="4">
         <v>58</v>
       </c>
@@ -30702,7 +30958,9 @@
       <c r="N195" s="6">
         <v>121</v>
       </c>
-      <c r="O195" s="6"/>
+      <c r="O195" s="6">
+        <v>78</v>
+      </c>
       <c r="P195" s="7">
         <v>5.6540178571428568</v>
       </c>
@@ -30712,31 +30970,75 @@
       <c r="R195" s="8">
         <v>9.6119653846153845</v>
       </c>
-      <c r="S195" s="8"/>
+      <c r="S195" s="8">
+        <v>7</v>
+      </c>
       <c r="T195" s="9">
         <v>0.20512820512820512</v>
       </c>
-      <c r="U195" s="9"/>
-      <c r="V195" s="9"/>
-      <c r="W195" s="9"/>
-      <c r="X195" s="9"/>
-      <c r="Y195" s="9"/>
-      <c r="Z195" s="9"/>
-      <c r="AA195" s="9"/>
-      <c r="AB195" s="9"/>
-      <c r="AC195" s="9"/>
-      <c r="AD195" s="6"/>
-      <c r="AE195" s="6"/>
-      <c r="AF195" s="6"/>
-      <c r="AG195" s="6"/>
-      <c r="AH195" s="6"/>
-      <c r="AI195" s="6"/>
-      <c r="AJ195" s="6"/>
-      <c r="AK195" s="6"/>
-      <c r="AL195" s="6"/>
-      <c r="AM195" s="6"/>
-      <c r="AN195" s="9"/>
-      <c r="AO195" s="6"/>
+      <c r="U195" s="9">
+        <v>0.064102564102564097</v>
+      </c>
+      <c r="V195" s="9">
+        <v>0</v>
+      </c>
+      <c r="W195" s="9">
+        <v>0</v>
+      </c>
+      <c r="X195" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y195" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z195" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA195" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB195" s="9">
+        <v>0.01282051282051282</v>
+      </c>
+      <c r="AC195" s="9">
+        <v>0.05128205128205128</v>
+      </c>
+      <c r="AD195" s="6">
+        <v>5</v>
+      </c>
+      <c r="AE195" s="6">
+        <v>5</v>
+      </c>
+      <c r="AF195" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG195" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH195" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI195" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ195" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK195" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL195" s="6">
+        <v>1</v>
+      </c>
+      <c r="AM195" s="6">
+        <v>4</v>
+      </c>
+      <c r="AN195" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO195" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP195" s="4">
         <v>58</v>
       </c>
